--- a/AAII_Financials/Yearly/ARCB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARCB_YR_FIN.xlsx
@@ -1014,7 +1014,7 @@
         <v>-60300</v>
       </c>
       <c r="F14" s="3">
-        <v>16600</v>
+        <v>17200</v>
       </c>
       <c r="G14" s="3">
         <v>5400</v>
@@ -1134,7 +1134,7 @@
         <v>4023300</v>
       </c>
       <c r="F17" s="3">
-        <v>4233800</v>
+        <v>4233200</v>
       </c>
       <c r="G17" s="3">
         <v>4628700</v>
@@ -1185,7 +1185,7 @@
         <v>155700</v>
       </c>
       <c r="F18" s="3">
-        <v>193700</v>
+        <v>194200</v>
       </c>
       <c r="G18" s="3">
         <v>400300</v>
@@ -1308,7 +1308,7 @@
         <v>285800</v>
       </c>
       <c r="F21" s="3">
-        <v>322400</v>
+        <v>323000</v>
       </c>
       <c r="G21" s="3">
         <v>515600</v>
